--- a/sim_output_tip.xlsx
+++ b/sim_output_tip.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,44 +495,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-08-20T00:55:22</t>
+          <t>2025-08-20T00:54:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tip_plane2_sat3</t>
+          <t>Tip_plane0_sat0</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.851327403042199</v>
+        <v>-45.29071381130465</v>
       </c>
       <c r="E2" t="n">
-        <v>-163.5020645750639</v>
+        <v>154.1147044796992</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-6921993.73847027</v>
+        <v>-3598988.28691545</v>
       </c>
       <c r="H2" t="n">
-        <v>123899.5731603805</v>
+        <v>3362292.686275035</v>
       </c>
       <c r="I2" t="n">
-        <v>895883.1207054679</v>
+        <v>-4971417.121436569</v>
       </c>
       <c r="J2" t="n">
-        <v>980.0576570336681</v>
+        <v>4842.629548844192</v>
       </c>
       <c r="K2" t="n">
-        <v>1026.680095687218</v>
+        <v>-2514.285671721932</v>
       </c>
       <c r="L2" t="n">
-        <v>7423.493120574577</v>
+        <v>-5212.895228334902</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -546,44 +546,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-08-20T00:58:22</t>
+          <t>2025-08-20T00:57:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tip_plane0_sat2</t>
+          <t>Tip_plane0_sat0</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-63.86437558707259</v>
+        <v>-54.53227824770108</v>
       </c>
       <c r="E3" t="n">
-        <v>-177.9363094240153</v>
+        <v>153.3416914796024</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-3121502.255897548</v>
+        <v>-2828878.517079301</v>
       </c>
       <c r="H3" t="n">
-        <v>856237.4892457981</v>
+        <v>2942999.639646032</v>
       </c>
       <c r="I3" t="n">
-        <v>-6190535.700886728</v>
+        <v>-5685027.051767532</v>
       </c>
       <c r="J3" t="n">
-        <v>6754.628022891799</v>
+        <v>5403.032600351952</v>
       </c>
       <c r="K3" t="n">
-        <v>462.7406051691293</v>
+        <v>-3063.998851139558</v>
       </c>
       <c r="L3" t="n">
-        <v>-3340.820531471483</v>
+        <v>-4281.35866006452</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -592,312 +592,6 @@
         <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>287</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-08-20T00:58:52</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tip_plane0_sat1</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>23.06234054496661</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-159.2293115251588</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-6361091.841275829</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-396078.8507253742</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2863274.769001864</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-3127.551519362436</v>
-      </c>
-      <c r="K4" t="n">
-        <v>941.5680173332349</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-6812.114673585269</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9.999999999999998</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>225</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025-08-20T00:59:22</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tip_plane0_sat1</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>22.31125746484529</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-160.1896020723324</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-6451556.251339503</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-367628.4184670579</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2657437.253672069</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-2902.875699657037</v>
-      </c>
-      <c r="K5" t="n">
-        <v>954.9614568645114</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-6909.18199579572</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>179</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025-08-20T01:01:52</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tip_plane2_sat3</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>31.86181654808652</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-168.3489003930057</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-5942778.819636475</v>
-      </c>
-      <c r="H6" t="n">
-        <v>501626.2502938964</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3626597.198376072</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3966.034227937172</v>
-      </c>
-      <c r="K6" t="n">
-        <v>881.5381996173224</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6371.109704669281</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-08-20T01:02:22</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tip_plane2_sat2</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-56.05310816803913</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-152.9916180633466</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-3844330.722298094</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-799388.1028340466</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-5777172.569731129</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-6313.239128060935</v>
-      </c>
-      <c r="K7" t="n">
-        <v>567.4017845966271</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4113.433896701633</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>256</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-08-20T01:03:52</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tip_plane3_sat3</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>61.24000140377193</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-89.8221164015533</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-841488.5092740011</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-3322966.08032065</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6082331.842907568</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-493.6234167258967</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6640.065599783908</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3561.002195229401</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>178</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025-08-20T01:08:52</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tip_plane2_sat3</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>57.82781169884332</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-176.5318781525685</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-3730625.002045371</v>
-      </c>
-      <c r="H9" t="n">
-        <v>808358.229483108</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5842054.197887991</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6385.249113090032</v>
-      </c>
-      <c r="K9" t="n">
-        <v>554.007551915337</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3996.995049073237</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1110,13 +804,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C958C5DA-B9E1-4DFC-AC60-A339775C037C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86DA3EB8-0DAB-493C-B5C7-2E8F13152D7D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE9366C3-6D3B-4C7A-84B3-1CAE5C9FD7D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74C8AE00-436C-4FC2-9C44-4ED3CA3B3595}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63E50D30-28FA-43E7-AA2D-403FF0AA4159}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F7E8BBC-4B43-40D0-9B27-FA88569B9405}"/>
 </file>
--- a/sim_output_tip.xlsx
+++ b/sim_output_tip.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,324 +493,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>238</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-08-20T00:54:52</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tip_plane0_sat0</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-45.29071381130465</v>
-      </c>
-      <c r="E2" t="n">
-        <v>154.1147044796992</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-3598988.28691545</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3362292.686275035</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-4971417.121436569</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4842.629548844192</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-2514.285671721932</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-5212.895228334902</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-08-20T00:57:22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tip_plane0_sat0</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-54.53227824770108</v>
-      </c>
-      <c r="E3" t="n">
-        <v>153.3416914796024</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-2828878.517079301</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2942999.639646032</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-5685027.051767532</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5403.032600351952</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-3063.998851139558</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-4281.35866006452</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F0CD86BD1575B641A929F0115BD08883" ma:contentTypeVersion="11" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="c7f378eef6aae23ec41cafa16c2d4f9c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ddbaa09c-6565-437b-9fe4-1fe08e886c94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e91425144512418e8a3dba2c78bb904b" ns2:_="">
-    <xsd:import namespace="ddbaa09c-6565-437b-9fe4-1fe08e886c94"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ddbaa09c-6565-437b-9fe4-1fe08e886c94" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Afbeeldingtags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b688d343-e684-46db-b94f-a4cae8ed196c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhoudstype"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddbaa09c-6565-437b-9fe4-1fe08e886c94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86DA3EB8-0DAB-493C-B5C7-2E8F13152D7D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74C8AE00-436C-4FC2-9C44-4ED3CA3B3595}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F7E8BBC-4B43-40D0-9B27-FA88569B9405}"/>
 </file>